--- a/BE/ca_lam_xtep.xlsx
+++ b/BE/ca_lam_xtep.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623FEB42-2C3E-4CB3-A4C5-C5BD278E753E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D0A8E0-3185-4EA7-827C-A8B3F5622152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,259 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="107">
+  <si>
+    <t>DANH SÁCH EMAIL CỬA HÀNG</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Cửa hàng</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Royal City</t>
+  </si>
+  <si>
+    <t>Vincom Việt Trì</t>
+  </si>
+  <si>
+    <t>Go Hạ Long</t>
+  </si>
+  <si>
+    <t>Time City</t>
+  </si>
+  <si>
+    <t>Ocean Park</t>
+  </si>
+  <si>
+    <t>Aeon Long Biên</t>
+  </si>
+  <si>
+    <t>Aeon Hải Phòng</t>
+  </si>
+  <si>
+    <t>Go Thái Nguyên</t>
+  </si>
+  <si>
+    <t>Aeon Hà Đông</t>
+  </si>
+  <si>
+    <t>Aeon Bình Dương</t>
+  </si>
+  <si>
+    <t>Vincom Thanh Hóa</t>
+  </si>
+  <si>
+    <t>Go Thái Bình</t>
+  </si>
+  <si>
+    <t>Go Nam Định</t>
+  </si>
+  <si>
+    <t>The Garden</t>
+  </si>
+  <si>
+    <t>Vincom Huế</t>
+  </si>
+  <si>
+    <t>VC Hạ Long</t>
+  </si>
+  <si>
+    <t>Nha Trang Center</t>
+  </si>
+  <si>
+    <t>Thiso Mall</t>
+  </si>
+  <si>
+    <t>Hùng Vương Plaza</t>
+  </si>
+  <si>
+    <t>Vincom Biên Hòa</t>
+  </si>
+  <si>
+    <t>Vincom Nha Trang</t>
+  </si>
+  <si>
+    <t>Vincom Đà Nẵng</t>
+  </si>
+  <si>
+    <t>Lotte Vũng Tàu</t>
+  </si>
+  <si>
+    <t>Sense Phạm Văn Đồng</t>
+  </si>
+  <si>
+    <t>Parc Mall</t>
+  </si>
+  <si>
+    <t>Lotte Phan Thiết</t>
+  </si>
+  <si>
+    <t>Aeon Huế</t>
+  </si>
+  <si>
+    <t>Vincom Trần Duy Hưng</t>
+  </si>
+  <si>
+    <t>Vincom Thảo Điền</t>
+  </si>
+  <si>
+    <t>Aeon Tân Phú</t>
+  </si>
+  <si>
+    <t>Lotte Đà Nẵng</t>
+  </si>
+  <si>
+    <t>Vạn Hạnh Mall</t>
+  </si>
+  <si>
+    <t>Vincom Bắc Ninh</t>
+  </si>
+  <si>
+    <t>Gold Coast Nha Trang</t>
+  </si>
+  <si>
+    <t>Aeon Tân An</t>
+  </si>
+  <si>
+    <t>A&amp;B Central</t>
+  </si>
+  <si>
+    <t>Aeon Bình Tân</t>
+  </si>
+  <si>
+    <t>Lotte Nha Trang</t>
+  </si>
+  <si>
+    <t>Vincom Vinh</t>
+  </si>
+  <si>
+    <t>vincomroyalcity@xtep.com</t>
+  </si>
+  <si>
+    <t>vcplazaviettri@xtep.com</t>
+  </si>
+  <si>
+    <t>xtephalong@xtep.com.</t>
+  </si>
+  <si>
+    <t>xteptimecity@xtep.com</t>
+  </si>
+  <si>
+    <t>vincomoceanpark@xtep.com</t>
+  </si>
+  <si>
+    <t>aeonmallhaiphong@xtep.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gothainguyen@xtep.com </t>
+  </si>
+  <si>
+    <t>aeonmallhadong@xtep.com.</t>
+  </si>
+  <si>
+    <t>aeonmallbinhduong@xtep.com</t>
+  </si>
+  <si>
+    <t>thanhhoavincomplaza@xtep.com</t>
+  </si>
+  <si>
+    <t>gothaibinh@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>gonamdinh@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>garden@xtep.com.cn.</t>
+  </si>
+  <si>
+    <t>huevincom@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>halongvincom@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>xtepnhatrangcenter@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>xtepthisomall@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>xtepkidlongbienaeon@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>hungvuongplaza@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>bienhoavc@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>nhatrangvc@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>danangvc@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>xtepparcmall@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>xteplottephanthiet@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>aeonhue@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>vincomthaodien@xtep.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xteplottevungtau@xtep.com.cn </t>
+  </si>
+  <si>
+    <t>xtepsensephamvandong@xtep.com.cn</t>
+  </si>
+  <si>
+    <t>tranduyhung@xtep.com</t>
+  </si>
+  <si>
+    <t>xtepaeonmalltanphu@xtep.com</t>
+  </si>
+  <si>
+    <t>xteplottedanang@xtep.com</t>
+  </si>
+  <si>
+    <t>xtepvanhanhmall@xtep.com</t>
+  </si>
+  <si>
+    <t>xtepvincombacninh@xtep.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> xtepbinhtan@gmail.com</t>
+  </si>
+  <si>
+    <t>Chưa có</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xtepgoldcoastnhatrang@xtep.com </t>
+  </si>
+  <si>
+    <t>Mật khẩu lỗi, k đăng nhập được</t>
+  </si>
+  <si>
+    <t>xteptanan239@gmail.com</t>
+  </si>
+  <si>
+    <t>Mail tự lập</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Ca làm</t>
+  </si>
   <si>
     <t>9:00 - 17:00
 14:00 - 22:00
@@ -39,9 +292,6 @@
     <t>8:00 - 16:00
 14:00 - 22:00
 12:00 - 20:00</t>
-  </si>
-  <si>
-    <t>Không có</t>
   </si>
   <si>
     <t>T2 - T6:
@@ -52,11 +302,10 @@
 14:00 - 22:00</t>
   </si>
   <si>
-    <t>8:00 - 16:00
-T2 - T5: 
-14:00 - 22:00
-T6 - CN: 
-14:30 - 22:30</t>
+    <t>Sáng: 8:00 - 16:00
+Chiều:
+T2 - T5: 14:00 - 22:00
+T6 - CN: 14:30 - 22:30</t>
   </si>
   <si>
     <t>T2 - T6:
@@ -78,7 +327,7 @@
 9:00 - 17:00
 14:00 - 22:00
 12:00 - 20:00
-T7 - CN:
+T7 - CN - Ngày lễ:
 8:30 - 16:30
 14:00 - 22:00
 12:00 - 20:00</t>
@@ -88,33 +337,42 @@
 14:00 - 22:00</t>
   </si>
   <si>
+    <t>Ca giữa lâu mới phát sinh 1 lần</t>
+  </si>
+  <si>
+    <t>T2 - T6:
+9:00 - 17:00
+14:00 - 22:00
+T7 - CN - Ngày lễ:
+8:30 - 16:30
+14:00 - 22:00</t>
+  </si>
+  <si>
     <t>7:30 - 15:30
 14:00 - 22:00
-11:00 - 19:00</t>
-  </si>
-  <si>
-    <t>Lỗi</t>
+12:00 - 20:00</t>
+  </si>
+  <si>
+    <t>8:00 - 16:00
+14:00 - 22:00</t>
   </si>
   <si>
     <t>T2 - T6:
 9:00 - 17:00
 14:00 - 22:00
 T7 - CN:
-8:30 - 16:30
-14:00 - 22:00</t>
-  </si>
-  <si>
-    <t>7:30 - 15:30
+8:00 - 16:00
 14:00 - 22:00
-12:00 - 20:00</t>
-  </si>
-  <si>
-    <t>8:00 - 16:00
-14:00 - 22:00</t>
+Ngày lễ:
+8:00 - 16:00
+14:30 - 22:30</t>
   </si>
   <si>
     <t>7:00 - 15:00
 14:00 - 22:00</t>
+  </si>
+  <si>
+    <t>Do cửa hàng đang thiếu NV nên ca sáng tăng ca: 17:00 - 19:00, chiều TC 12:00 - 14:00, chủ nhật có 1 bạn làm full 9:00 -22:00</t>
   </si>
   <si>
     <t>9:00 - 17:00
@@ -122,6 +380,9 @@
 12:00 - 20:00</t>
   </si>
   <si>
+    <t>Ca đêm hàng về nhiều làm từ 22:00 - trễ nhất 4h sáng</t>
+  </si>
+  <si>
     <t>8:30 - 16:30
 14:00 - 22:00
 12:00 - 20:00</t>
@@ -132,121 +393,43 @@
 12:00 - 20:00</t>
   </si>
   <si>
-    <t>1. ROYAL</t>
-  </si>
-  <si>
-    <t>3. VC Việt Trì</t>
-  </si>
-  <si>
-    <t>4. GO Hạ Long</t>
-  </si>
-  <si>
-    <t>6. Time City</t>
-  </si>
-  <si>
-    <t>8. Ocean Park</t>
-  </si>
-  <si>
-    <t>11. GO Thái Nguyên</t>
-  </si>
-  <si>
-    <t>12. AEON Hà Đông</t>
-  </si>
-  <si>
-    <t>13. AEON Bình Dương</t>
-  </si>
-  <si>
-    <t>14. VC Thanh Hóa</t>
-  </si>
-  <si>
-    <t>18. GO Thái Bình</t>
-  </si>
-  <si>
-    <t>19. GO Nam Định</t>
-  </si>
-  <si>
-    <t>21. The Garden</t>
-  </si>
-  <si>
-    <t>22. VC Huế</t>
-  </si>
-  <si>
-    <t>23. VC Hạ Long</t>
-  </si>
-  <si>
-    <t>24. Nha Trang Center</t>
-  </si>
-  <si>
-    <t>25. THISO Mall</t>
-  </si>
-  <si>
-    <t>26. Aeon Long Biên</t>
-  </si>
-  <si>
-    <t>27. Hùng Vương Plaza</t>
-  </si>
-  <si>
-    <t>28. VC Biên Hòa</t>
-  </si>
-  <si>
-    <t>29. VC Nha Trang</t>
-  </si>
-  <si>
-    <t>30. VC Đà Nẵng</t>
-  </si>
-  <si>
-    <t>32. LOTTE Vũng Tàu</t>
-  </si>
-  <si>
-    <t>33. Sense Phạm Văn Đồng</t>
-  </si>
-  <si>
-    <t>35. LOTTE Phan Thiết</t>
-  </si>
-  <si>
-    <t>37. VC Trần Duy Hưng</t>
-  </si>
-  <si>
-    <t>38. VC Thảo Điền</t>
-  </si>
-  <si>
-    <t>39. Aeon mall Tân Phú</t>
-  </si>
-  <si>
-    <t>40. LOTTE Đà Nẵng</t>
-  </si>
-  <si>
-    <t>41. Vạn Hạnh Mall</t>
-  </si>
-  <si>
-    <t>42. Vincom Bắc Ninh</t>
-  </si>
-  <si>
-    <t>43.Gold Coast Nha Trang</t>
-  </si>
-  <si>
-    <t>44. Aeon Tân An</t>
-  </si>
-  <si>
-    <t>46. Aeon Bình Tân</t>
-  </si>
-  <si>
-    <t>47. Lotte Nha Trang</t>
-  </si>
-  <si>
-    <t>Cửa hàng</t>
-  </si>
-  <si>
-    <t>Ca làm</t>
+    <t>T2 - T6:
+9:00 - 17:00
+14:00 - 22:00
+12:00 - 20:00
+T7 - CN:
+8:00 - 16:00
+14:00 - 22:00
+12:00 - 20:00
+Lễ: 
+8:00 - 16:00
+14:30 - 22:30
+12:00 - 20:00</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>7:30 - 15:30
+14:00 - 22:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -288,11 +471,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -309,6 +502,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1109473</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>533401</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5934076" y="9582151"/>
+          <a:ext cx="1109472" cy="533400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,331 +816,1016 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:F43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>18</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>19</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>24</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>25</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>26</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>27</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>28</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>31</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>32</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>33</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>34</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>35</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>36</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>37</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>38</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>39</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4CA2C1-2903-4174-87BB-E4C1F18BFE26}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68" customWidth="1"/>
-    <col min="2" max="2" width="103.140625" customWidth="1"/>
+    <col min="1" max="1" width="64" customWidth="1"/>
+    <col min="2" max="2" width="68.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="210" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="225" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B21" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B22" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B23" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B24" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="225" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B25" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B26" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="210" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B27" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B28" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B29" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B30" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="225" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B31" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B32" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B33" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B34" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="210" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B36" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B37" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B38" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B39" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>0</v>
+      <c r="B40" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/BE/ca_lam_xtep.xlsx
+++ b/BE/ca_lam_xtep.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6A6178-737A-48E8-A60F-9FCCE19EBA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEF6208-AEF7-4142-A89D-205814AA5D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="16410" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -30,9 +30,6 @@
     <t>Cửa hàng</t>
   </si>
   <si>
-    <t>Royal City</t>
-  </si>
-  <si>
     <t>Vincom Việt Trì</t>
   </si>
   <si>
@@ -270,6 +267,9 @@
   <si>
     <t>7:30 - 15:30
 14:00 - 22:00</t>
+  </si>
+  <si>
+    <t>Royal</t>
   </si>
 </sst>
 </file>
@@ -620,319 +620,319 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="180" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/BE/ca_lam_xtep.xlsx
+++ b/BE/ca_lam_xtep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEF6208-AEF7-4142-A89D-205814AA5D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492B5DBF-5DEF-4C86-AE62-1D7943E27349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="16410" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -30,9 +30,6 @@
     <t>Cửa hàng</t>
   </si>
   <si>
-    <t>Vincom Việt Trì</t>
-  </si>
-  <si>
     <t>Go Hạ Long</t>
   </si>
   <si>
@@ -57,9 +54,6 @@
     <t>Aeon Bình Dương</t>
   </si>
   <si>
-    <t>Vincom Thanh Hóa</t>
-  </si>
-  <si>
     <t>Go Thái Bình</t>
   </si>
   <si>
@@ -69,9 +63,6 @@
     <t>The Garden</t>
   </si>
   <si>
-    <t>Vincom Huế</t>
-  </si>
-  <si>
     <t>VC Hạ Long</t>
   </si>
   <si>
@@ -84,39 +75,18 @@
     <t>Hùng Vương Plaza</t>
   </si>
   <si>
-    <t>Vincom Biên Hòa</t>
-  </si>
-  <si>
-    <t>Vincom Nha Trang</t>
-  </si>
-  <si>
-    <t>Vincom Đà Nẵng</t>
-  </si>
-  <si>
     <t>Lotte Vũng Tàu</t>
   </si>
   <si>
     <t>Sense Phạm Văn Đồng</t>
   </si>
   <si>
-    <t>Parc Mall</t>
-  </si>
-  <si>
     <t>Lotte Phan Thiết</t>
   </si>
   <si>
     <t>Aeon Huế</t>
   </si>
   <si>
-    <t>Vincom Trần Duy Hưng</t>
-  </si>
-  <si>
-    <t>Vincom Thảo Điền</t>
-  </si>
-  <si>
-    <t>Aeon Tân Phú</t>
-  </si>
-  <si>
     <t>Lotte Đà Nẵng</t>
   </si>
   <si>
@@ -139,9 +109,6 @@
   </si>
   <si>
     <t>Lotte Nha Trang</t>
-  </si>
-  <si>
-    <t>Vincom Vinh</t>
   </si>
   <si>
     <t>Ca làm</t>
@@ -270,6 +237,39 @@
   </si>
   <si>
     <t>Royal</t>
+  </si>
+  <si>
+    <t>VC Việt Trì</t>
+  </si>
+  <si>
+    <t>VC Thanh Hóa</t>
+  </si>
+  <si>
+    <t>VC Huế</t>
+  </si>
+  <si>
+    <t>VC Biên Hòa</t>
+  </si>
+  <si>
+    <t>VC Nha Trang</t>
+  </si>
+  <si>
+    <t>VC Đà Nẵng</t>
+  </si>
+  <si>
+    <t>Parc Mall - HCM</t>
+  </si>
+  <si>
+    <t>VC Trần Duy Hưng</t>
+  </si>
+  <si>
+    <t>VC Thảo Điền</t>
+  </si>
+  <si>
+    <t>Aeon mall Tân Phú</t>
+  </si>
+  <si>
+    <t>VC Vinh</t>
   </si>
 </sst>
 </file>
@@ -620,319 +620,319 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="180" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/BE/ca_lam_xtep.xlsx
+++ b/BE/ca_lam_xtep.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\GitHub\XTEP_Web\BE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492B5DBF-5DEF-4C86-AE62-1D7943E27349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7948AABA-466F-4924-A61A-6F5BEC1C104C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="67">
   <si>
     <t>Cửa hàng</t>
   </si>
@@ -232,44 +232,77 @@
 12:00 - 20:00</t>
   </si>
   <si>
-    <t>7:30 - 15:30
+    <t>Royal</t>
+  </si>
+  <si>
+    <t>VC Việt Trì</t>
+  </si>
+  <si>
+    <t>VC Thanh Hóa</t>
+  </si>
+  <si>
+    <t>VC Huế</t>
+  </si>
+  <si>
+    <t>VC Biên Hòa</t>
+  </si>
+  <si>
+    <t>VC Nha Trang</t>
+  </si>
+  <si>
+    <t>VC Đà Nẵng</t>
+  </si>
+  <si>
+    <t>Parc Mall - HCM</t>
+  </si>
+  <si>
+    <t>VC Trần Duy Hưng</t>
+  </si>
+  <si>
+    <t>VC Thảo Điền</t>
+  </si>
+  <si>
+    <t>Aeon mall Tân Phú</t>
+  </si>
+  <si>
+    <t>VC Vinh</t>
+  </si>
+  <si>
+    <t>8:00-16:00
 14:00 - 22:00</t>
   </si>
   <si>
-    <t>Royal</t>
-  </si>
-  <si>
-    <t>VC Việt Trì</t>
-  </si>
-  <si>
-    <t>VC Thanh Hóa</t>
-  </si>
-  <si>
-    <t>VC Huế</t>
-  </si>
-  <si>
-    <t>VC Biên Hòa</t>
-  </si>
-  <si>
-    <t>VC Nha Trang</t>
-  </si>
-  <si>
-    <t>VC Đà Nẵng</t>
-  </si>
-  <si>
-    <t>Parc Mall - HCM</t>
-  </si>
-  <si>
-    <t>VC Trần Duy Hưng</t>
-  </si>
-  <si>
-    <t>VC Thảo Điền</t>
-  </si>
-  <si>
-    <t>Aeon mall Tân Phú</t>
-  </si>
-  <si>
-    <t>VC Vinh</t>
+    <t>8:00 - 16:00
+12:00 - 20:00
+14:00 - 22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2 - T6
+9:00 - 17:00
+14:00 - 22:00
+12:00 - 20:00
+T7 - CN
+8:00 - 16:00
+14:00 - 22:00
+12:00 - 20:00
+</t>
+  </si>
+  <si>
+    <t>7:00 - 15:00
+12:00 - 20:00
+14:00 - 22:00</t>
+  </si>
+  <si>
+    <t>Vincom Đan Phượng</t>
+  </si>
+  <si>
+    <t>VC Skylake</t>
+  </si>
+  <si>
+    <t>CH Tasco Mall</t>
+  </si>
+  <si>
+    <t>MM Đà nẵng</t>
   </si>
 </sst>
 </file>
@@ -608,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4CA2C1-2903-4174-87BB-E4C1F18BFE26}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
@@ -625,7 +658,7 @@
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
@@ -633,7 +666,7 @@
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>30</v>
@@ -697,7 +730,7 @@
     </row>
     <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>29</v>
@@ -729,7 +762,7 @@
     </row>
     <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -777,7 +810,7 @@
     </row>
     <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
@@ -785,7 +818,7 @@
     </row>
     <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -793,7 +826,7 @@
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>37</v>
@@ -804,7 +837,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -817,7 +850,7 @@
     </row>
     <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>38</v>
@@ -841,7 +874,7 @@
     </row>
     <row r="29" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>29</v>
@@ -849,7 +882,7 @@
     </row>
     <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>29</v>
@@ -857,7 +890,7 @@
     </row>
     <row r="31" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>41</v>
@@ -929,9 +962,41 @@
     </row>
     <row r="40" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>29</v>
       </c>
     </row>
